--- a/output/full_scan/batch_seq0_2026-09-04.xlsx
+++ b/output/full_scan/batch_seq0_2026-09-04.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1096.031542689522</v>
+        <v>1236.031542689522</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>10.4</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.14482828094359</v>
+        <v>59.14482573531527</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22.93422906149136</v>
+        <v>22.93422760053894</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.501792878985479</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0239458471936876</v>
+        <v>0.0239458493687442</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>839</v>
+        <v>1039</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>68.8</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>81.74240443781682</v>
+        <v>81.7424044665288</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.46060742339729</v>
+        <v>25.46060743853351</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>7.878064937907173</v>
@@ -623,11 +623,11 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.361502402491243</v>
+        <v>2.361502402367231</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>755.6632611358657</v>
+        <v>925.6632611358654</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>135</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.44439305627049</v>
+        <v>60.44439311608474</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21.03443168261307</v>
+        <v>21.03443174422801</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.189097594232201</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.692684351019112</v>
+        <v>1.69268435054212</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>727.416299870564</v>
+        <v>897.416299870564</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>112</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.17799842766109</v>
+        <v>58.17799844441501</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.49126181305036</v>
+        <v>15.49126183254503</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>4.129905366589084</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.786766140412029</v>
+        <v>1.786766140230763</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8423</v>
+        <v>8240</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>714.4813771190596</v>
+        <v>866.6503134554789</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18.2</v>
+        <v>51.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.64243075368898</v>
+        <v>66.33713586453922</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.51496439528798</v>
+        <v>26.39205842877957</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.048137711905961</v>
+        <v>2.265031345547889</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0306963522041344</v>
+        <v>1.068769596165226</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8240</v>
+        <v>8996</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>666.6503134554789</v>
+        <v>847.9137816178641</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>51.5</v>
+        <v>1300</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.33713584196886</v>
+        <v>57.59393356309723</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.39205840708162</v>
+        <v>19.7207199969529</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.265031345547889</v>
+        <v>1.581949788286152</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.068769596231998</v>
+        <v>8.775489023715011</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8155</v>
+        <v>8423</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>653.5044538179447</v>
+        <v>829.4813771190596</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>348.5</v>
+        <v>18.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.3888985551188</v>
+        <v>61.64243038894665</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.39073589444675</v>
+        <v>25.51496436347982</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6806320947388932</v>
+        <v>1.048137711905961</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.137796019647967</v>
+        <v>0.0306963522899918</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8085</v>
+        <v>9105</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>647.6681897507104</v>
+        <v>790.4165538643366</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.2</v>
+        <v>8.65</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>66.7666614216661</v>
+        <v>55.12566779010618</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30.28705994868823</v>
+        <v>18.88998665096362</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5159957711630728</v>
+        <v>0.8613636233198325</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2079231673447057</v>
+        <v>0.036074201225622</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8271</v>
+        <v>8103</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>610.1883483450432</v>
+        <v>786.507236361873</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>217</v>
+        <v>122.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>44.245334192984</v>
+        <v>72.2680793666629</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.94373258254012</v>
+        <v>43.83260384010656</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4572105957722779</v>
+        <v>1.150723636187302</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-2.609738459606717</v>
+        <v>2.995675876067414</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8103</v>
+        <v>8442</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>596.5072363618731</v>
+        <v>778.9690972969599</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>122.5</v>
+        <v>45.55</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>72.26807934116101</v>
+        <v>51.79781948888752</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>43.8326038570057</v>
+        <v>15.93053978274086</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.150723636187302</v>
+        <v>0.2042988087515118</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.995675876296295</v>
+        <v>-0.1497872949408866</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8996</v>
+        <v>8111</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>592.9137816178641</v>
+        <v>694.9307089031034</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1300</v>
+        <v>70</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.59393355524877</v>
+        <v>59.12559334144205</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>19.72071997069092</v>
+        <v>26.68950048070231</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.581949788286152</v>
+        <v>1.375127282230974</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>8.775489024955462</v>
+        <v>1.00646165195357</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>9912</v>
+        <v>8926</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>576.6886181545148</v>
+        <v>691.2084724121232</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12.95</v>
+        <v>57.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>51.96619309794787</v>
+        <v>44.67038812977897</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.23904469268547</v>
+        <v>29.55713589072234</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4298980773391311</v>
+        <v>0.5925055423128377</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.0302785611361012</v>
+        <v>0.4753695036309695</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9105</v>
+        <v>8482</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>575.4165538643366</v>
+        <v>680.2137023629181</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8.65</v>
+        <v>48.45</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.12566774529686</v>
+        <v>51.22943103498724</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18.88998662790769</v>
+        <v>3.860179498979657</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.8613636233198325</v>
+        <v>1.643403507240775</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,11 +1206,11 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0360742012351623</v>
+        <v>-0.1562969240493485</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>564.5399672679055</v>
+        <v>679.5399672679055</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>110.5</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>49.56530125970213</v>
+        <v>49.56530126457543</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18.76131134880687</v>
+        <v>18.76131137582105</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.617316340041727</v>
@@ -1259,11 +1259,11 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.93820053269482</v>
+        <v>1.938200532628033</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>554.0779019760944</v>
+        <v>669.0779019760937</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>41</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.8444511001798</v>
+        <v>55.84445114672646</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.79250798749621</v>
+        <v>31.79250800010146</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.5124496437502228</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0486750659031599</v>
+        <v>0.0486750658936246</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8482</v>
+        <v>8155</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>545.2137023629183</v>
+        <v>653.5044538179449</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>48.45</v>
+        <v>348.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>51.22943102521696</v>
+        <v>55.38889860606692</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3.860179449168833</v>
+        <v>22.39073592173943</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.643403507240775</v>
+        <v>0.6806320947388932</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1562969237059217</v>
+        <v>3.137796019170949</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8299</v>
+        <v>8085</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>538.7048304981593</v>
+        <v>647.6681897507104</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2015</v>
+        <v>15.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>47.31407107509867</v>
+        <v>66.76666150781624</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10.97295972169903</v>
+        <v>30.28705997947795</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5162767822266042</v>
+        <v>0.5159957711630728</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-8.127885829554568</v>
+        <v>0.2079231672493102</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8150</v>
+        <v>8080</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>516.0075671911459</v>
+        <v>637.481978485439</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>28.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>49.49684131451543</v>
+        <v>57.24922323758929</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.69774122868458</v>
+        <v>56.14238347734925</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5043034630960052</v>
+        <v>1.158114187483998</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4343074279609831</v>
+        <v>0.1044013301045249</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8043</v>
+        <v>8429</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>506.5579111629617</v>
+        <v>612.4470533449196</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>142</v>
+        <v>6.04</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>49.68496014898027</v>
+        <v>48.7080978494082</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>12.74429645325878</v>
+        <v>8.420762550388581</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.01643848641976</v>
+        <v>0.6842800819259786</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.8125712790451769</v>
+        <v>0.0074205388008046</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8093</v>
+        <v>8271</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>503.6801878715148</v>
+        <v>595.1883483450431</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>26.35</v>
+        <v>217</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.01130620832416</v>
+        <v>44.24533419912896</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>19.63537008030627</v>
+        <v>20.94373258047164</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.1926931816052947</v>
+        <v>0.4572105957722779</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.1072488842867049</v>
+        <v>-2.609738459683037</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8462</v>
+        <v>9912</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>497.6926032667476</v>
+        <v>576.6886181545148</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>165.5</v>
+        <v>12.95</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>44.17237239253447</v>
+        <v>51.96619312034783</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>29.88035339739382</v>
+        <v>20.23904481605008</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6569094725983506</v>
+        <v>0.4298980773391311</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.849502623912087</v>
+        <v>-0.0302785611265614</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8080</v>
+        <v>8299</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>497.4819784854401</v>
+        <v>538.7048304981593</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>28.8</v>
+        <v>2015</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.24922333604329</v>
+        <v>47.31407107509867</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>56.14238319596785</v>
+        <v>10.97295972483288</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.158114187483998</v>
+        <v>0.5162767822266042</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1044013299805082</v>
+        <v>-8.127885829268287</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8111</v>
+        <v>9802</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>494.9307089031034</v>
+        <v>518.2176422387433</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>70</v>
+        <v>72.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>59.1255933115234</v>
+        <v>50.88846443970053</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.68950042975321</v>
+        <v>9.356309788383079</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.375127282230974</v>
+        <v>0.6975663484061568</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.006461652163444</v>
+        <v>0.1531239683064197</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>9930</v>
+        <v>8150</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>481.2668308313849</v>
+        <v>516.0075671911459</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>63.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>48.04794995473397</v>
+        <v>49.49684132092028</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.59977195615858</v>
+        <v>11.69774126592633</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.049748477285365</v>
+        <v>0.5043034630960052</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0240441844598549</v>
+        <v>0.4343074278560433</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8926</v>
+        <v>8464</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>461.2084724121232</v>
+        <v>508.8109537311779</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>57.5</v>
+        <v>373.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>44.67038810484033</v>
+        <v>51.74312820451288</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>29.55713591281886</v>
+        <v>16.67832326832475</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5925055423128377</v>
+        <v>0.3782588980851703</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.475369503602348</v>
+        <v>-0.4738174783853638</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8442</v>
+        <v>8043</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>458.9690972969597</v>
+        <v>506.5579111629617</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45.55</v>
+        <v>142</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.79781880813386</v>
+        <v>49.6849601599575</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15.93053973754716</v>
+        <v>12.74429650597206</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2042988087515118</v>
+        <v>1.01643848641976</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.1497872933382159</v>
+        <v>0.8125712788352906</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8109</v>
+        <v>8093</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>456.7555281375409</v>
+        <v>503.6801878715148</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>130</v>
+        <v>26.35</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,102 +1930,102 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.14631386031304</v>
+        <v>56.01130617000744</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.79837518344684</v>
+        <v>19.63537001305013</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6961544060156056</v>
+        <v>0.1926931816052947</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0191055126448943</v>
+        <v>-0.107248884188611</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>9110</v>
+        <v>8215</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>444.2250423880906</v>
+        <v>501.8421758511525</v>
       </c>
       <c r="E29" s="2" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>53.20803978485917</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>23.39722718925149</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1.082172950478202</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>51.54175691066365</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>6.387015817458225</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>5.170819467946581</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0138926002425385</v>
+        <v>0.2227475113085262</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8069</v>
+        <v>9930</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>441.8152137820334</v>
+        <v>501.2668308313849</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>148.5</v>
+        <v>63.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>31.70713346637328</v>
+        <v>48.04794992766428</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.8712941229291</v>
+        <v>26.59977191456115</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5964130671976929</v>
+        <v>1.049748477285365</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.3739893341727551</v>
+        <v>0.0240441844407657</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8182</v>
+        <v>8462</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>440.2001075693186</v>
+        <v>497.6926032667476</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>38.85</v>
+        <v>165.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.9698200741751</v>
+        <v>44.17237258782558</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>9.54033067171266</v>
+        <v>29.88035341018932</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2561128381654489</v>
+        <v>0.6569094725983506</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.018208998770097</v>
+        <v>-1.849502624293669</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8054</v>
+        <v>8109</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>429.2997192029073</v>
+        <v>456.7555281375409</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>82.5</v>
+        <v>130</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45.64780114610036</v>
+        <v>49.14631385636286</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.34020446049242</v>
+        <v>19.79837505360796</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.567168884749225</v>
+        <v>0.6961544060156056</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.6681022872331219</v>
+        <v>-0.0191055126067518</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8097</v>
+        <v>9110</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>419.9909232648349</v>
+        <v>444.2250423880906</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>32.71280384019228</v>
+        <v>51.54175690882174</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.79775418853468</v>
+        <v>6.387015900050018</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.18503290427619</v>
+        <v>5.170819467946581</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1036777702335283</v>
+        <v>-0.0138926002444459</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8473</v>
+        <v>8069</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>407.3697384455533</v>
+        <v>441.8152137820332</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45.7</v>
+        <v>148.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.98130960998486</v>
+        <v>31.70713351174787</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.85063065117332</v>
+        <v>22.8712942071429</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.08919842118993</v>
+        <v>0.5964130671976929</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1184214793098171</v>
+        <v>-0.3739893338865485</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8222</v>
+        <v>8182</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>404.5931520092208</v>
+        <v>440.2001075693186</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>37</v>
+        <v>38.85</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>42.25905747859136</v>
+        <v>43.96982007885043</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.95648551750897</v>
+        <v>9.54033067566762</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3695323439627935</v>
+        <v>0.2561128381654489</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.333447540504556</v>
+        <v>-0.0182089987796377</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8050</v>
+        <v>8054</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>403.4015011715007</v>
+        <v>429.2997192029072</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>56.4</v>
+        <v>82.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46.47598767717675</v>
+        <v>45.64780128615613</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10.27742227725149</v>
+        <v>14.34020444548645</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4035245607018512</v>
+        <v>0.567168884749225</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>1</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2651109372526633</v>
+        <v>0.6681022864699391</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8112</v>
+        <v>8097</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>403.0635268789543</v>
+        <v>419.9909232648349</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>90.5</v>
+        <v>49</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.99928325951414</v>
+        <v>32.71280394021309</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9.602872738971836</v>
+        <v>29.79775422102756</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3575867222563454</v>
+        <v>1.18503290427619</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.5765778329211262</v>
+        <v>0.10367777040524</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8464</v>
+        <v>8222</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>393.8109537311782</v>
+        <v>419.5931520092208</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>373.5</v>
+        <v>37</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.74312815801439</v>
+        <v>42.25905755954395</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.67832325388524</v>
+        <v>21.95648556562143</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3782588980851703</v>
+        <v>0.3695323439627935</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.4738174781945787</v>
+        <v>-0.3334475407430457</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8443</v>
+        <v>9103</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>391.631028865003</v>
+        <v>416.9633976814756</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11.15</v>
+        <v>5.14</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>34.89437852350363</v>
+        <v>49.03352195398463</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46.14088499612564</v>
+        <v>8.738759876562934</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3124945973860981</v>
+        <v>0.6997929943649973</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0233396491284334</v>
+        <v>-0.005942840576958</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8163</v>
+        <v>8455</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>390.5017465983577</v>
+        <v>408.4828952702093</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>31.5</v>
+        <v>22.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46.97638251764185</v>
+        <v>49.39292941667251</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>13.19485312641282</v>
+        <v>11.87655615318549</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9046417412078624</v>
+        <v>2.793104953087497</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2020115804742422</v>
+        <v>0.2159228063302984</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8291</v>
+        <v>8473</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>388.2003402506483</v>
+        <v>407.3697384455533</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>29.9</v>
+        <v>45.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>36.94532142960336</v>
+        <v>53.98130959944959</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10.3427260874075</v>
+        <v>26.85063071972512</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6024981043137616</v>
+        <v>1.08919842118993</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.255937897255349</v>
+        <v>0.1184214793575166</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8261</v>
+        <v>8050</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>387.6788936914363</v>
+        <v>403.4015011715007</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>180.5</v>
+        <v>56.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45.20464737887443</v>
+        <v>46.47598769074161</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12.36982636191014</v>
+        <v>10.27742228753899</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5605299945955626</v>
+        <v>0.4035245607018512</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.580183396267154</v>
+        <v>-0.2651109373480574</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8429</v>
+        <v>8112</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>387.4470533449197</v>
+        <v>403.0635268789543</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>6.04</v>
+        <v>90.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>48.70809779665535</v>
+        <v>48.99928327437006</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>8.420762572828203</v>
+        <v>9.602872748669766</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6842800819259786</v>
+        <v>0.3575867222563454</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.007420538812252</v>
+        <v>-0.5765778329974437</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8215</v>
+        <v>8261</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>386.8421758511525</v>
+        <v>402.6788936914363</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>25.55</v>
+        <v>180.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.20803975381572</v>
+        <v>45.20464738823552</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.39722722999723</v>
+        <v>12.36982636191014</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.082172950478202</v>
+        <v>0.5605299945955626</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2227475113657653</v>
+        <v>1.580183396095416</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8289</v>
+        <v>8443</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>385.8836410163001</v>
+        <v>391.631028865003</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>44.5</v>
+        <v>11.15</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.54180660609848</v>
+        <v>34.89437843740811</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.84250205771845</v>
+        <v>46.14088505331519</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4513221703491832</v>
+        <v>0.3124945973860981</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1029151801149703</v>
+        <v>-0.0233396491188931</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8101</v>
+        <v>8163</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>377.8273423842658</v>
+        <v>390.5017465983577</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>12</v>
+        <v>31.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.1082601491775</v>
+        <v>46.97638252316399</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6.691858664122766</v>
+        <v>13.19485311764748</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4051873742106109</v>
+        <v>0.9046417412078624</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.037024809838741</v>
+        <v>0.2020115804742422</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2912,21 +2912,21 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8171</v>
+        <v>8291</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>374.7526445649683</v>
+        <v>388.2003402506483</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>19.55</v>
+        <v>29.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.01882871899336</v>
+        <v>36.94500227225253</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>12.0521165827353</v>
+        <v>10.34550064118259</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8341107210402424</v>
+        <v>0.6024981043137616</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.009177672335512799</v>
+        <v>-0.2559364112818951</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8411</v>
+        <v>8289</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>373.4661165778201</v>
+        <v>385.8836410163001</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>13</v>
+        <v>44.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.56704068677141</v>
+        <v>43.54180662220717</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14.1652776111261</v>
+        <v>18.84250211371128</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6468423539963923</v>
+        <v>0.4513221703491832</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0059880546969294</v>
+        <v>0.1029151801245039</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8234</v>
+        <v>8101</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>370.1894836852993</v>
+        <v>377.827342384266</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>68.3</v>
+        <v>12</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.30838007816355</v>
+        <v>50.10826016672743</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.7738194485025</v>
+        <v>6.691858680262329</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5877629420753986</v>
+        <v>0.4051873742106109</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.1467006135804362</v>
+        <v>0.0370248098101207</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8438</v>
+        <v>8171</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>359.3177365183482</v>
+        <v>374.7526445649683</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>68.8</v>
+        <v>19.55</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.01023731037976</v>
+        <v>44.0188287939113</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16.71257241968603</v>
+        <v>12.05211658273531</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.819478547564582</v>
+        <v>0.8341107210402424</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.6677422498981742</v>
+        <v>0.0091776723164342</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8105</v>
+        <v>8411</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>354.6192159154302</v>
+        <v>373.4661165778201</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>41.20162371758779</v>
+        <v>54.56704074640008</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.31002324718999</v>
+        <v>14.1652776111261</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6749262908913817</v>
+        <v>0.6468423539963923</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0299766662287765</v>
+        <v>-0.0059880546969294</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8096</v>
+        <v>8234</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>347.5023175904806</v>
+        <v>370.1894836852992</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>104.5</v>
+        <v>68.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>36.79313248726612</v>
+        <v>52.3083801243956</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.43680075060572</v>
+        <v>16.77381945758431</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4023565223458747</v>
+        <v>0.5877629420753986</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>1</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.383768776096943</v>
+        <v>-0.1467006138093953</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8183</v>
+        <v>8162</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>342.2663593733357</v>
+        <v>369.6502593002104</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>27.8</v>
+        <v>60.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>34.5722163027917</v>
+        <v>49.48047165711681</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.8610868241399</v>
+        <v>16.17912362247176</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.96867509125322</v>
+        <v>0.341783894550288</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0457726530380884</v>
+        <v>0.248763537199869</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8383</v>
+        <v>8438</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>338.5428384186545</v>
+        <v>359.3177365183482</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>65.2</v>
+        <v>68.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.04961504636424</v>
+        <v>47.01023732612099</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11.00047872002715</v>
+        <v>16.7125724331582</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3744324458858838</v>
+        <v>0.819478547564582</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>1</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1521542222370393</v>
+        <v>0.6677422499077104</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8102</v>
+        <v>9904</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>334.880199742775</v>
+        <v>355.5382044114963</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>65</v>
+        <v>24.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.07463582806018</v>
+        <v>49.40464646278409</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7.995524286852419</v>
+        <v>17.39127736645623</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.1745606689777569</v>
+        <v>0.363611452817673</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.6663644343108741</v>
+        <v>-0.0142369883953666</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8070</v>
+        <v>8105</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>332.5927995438497</v>
+        <v>354.6192159154302</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>50.5</v>
+        <v>15</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.37414753031701</v>
+        <v>41.20162350524356</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.99171530516526</v>
+        <v>26.31002326995774</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3688507308270164</v>
+        <v>0.6749262908913817</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0471160965508522</v>
+        <v>0.0299766666223733</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8114</v>
+        <v>8472</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>331.1983370892369</v>
+        <v>353.0721713954265</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>194.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.45648841207245</v>
+        <v>56.21829450175317</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.76504069084909</v>
+        <v>16.78297575046203</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5488164779930813</v>
+        <v>0.5701676863165457</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.5976841888319306</v>
+        <v>0.5367731175566102</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8081</v>
+        <v>8481</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>330.9335776669601</v>
+        <v>347.5933137367206</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>254.5</v>
+        <v>41</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.21201822036972</v>
+        <v>52.07163154581223</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.35835521535726</v>
+        <v>12.54643171124082</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4230769927137641</v>
+        <v>1.448043467280481</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1238700068383096</v>
+        <v>0.0203732446400729</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8074</v>
+        <v>8096</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>330.8895585119031</v>
+        <v>347.5023175904806</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>53.3</v>
+        <v>104.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.11775922218957</v>
+        <v>36.79313251577372</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>14.54973040596056</v>
+        <v>21.43680080188179</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.56942738539106</v>
+        <v>0.4023565223458747</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0514017263623325</v>
+        <v>0.3837687760492452</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8440</v>
+        <v>8087</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>328.7443273256742</v>
+        <v>344.7197812570221</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>20.2</v>
+        <v>27</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.01900470353816</v>
+        <v>50.97603903445914</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.79250109679266</v>
+        <v>6.927590316997606</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5139961854855799</v>
+        <v>0.2212650734342542</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0008814034224432</v>
+        <v>0.070502330161966</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8481</v>
+        <v>8183</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>327.5933137367207</v>
+        <v>342.2663593733358</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>41</v>
+        <v>27.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.07163154581223</v>
+        <v>34.57221648597383</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.54643163086482</v>
+        <v>21.86108684496441</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.448043467280481</v>
+        <v>2.96867509125322</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0203732445923748</v>
+        <v>-0.0457726533242818</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8086</v>
+        <v>8383</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>321.6648800312741</v>
+        <v>338.5428384186545</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>112.5</v>
+        <v>65.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.51685413719022</v>
+        <v>44.04961501508203</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.80138393602065</v>
+        <v>11.00047882100213</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5397824652365338</v>
+        <v>0.3744324458858838</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4275037632903875</v>
+        <v>-0.1521542224087568</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8110</v>
+        <v>8102</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>320.3516906715813</v>
+        <v>334.880199742775</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>43.55</v>
+        <v>65</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.29064643505671</v>
+        <v>50.07463580298366</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>8.574052932803234</v>
+        <v>7.995524289199171</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5519939799360098</v>
+        <v>0.1745606689777569</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0835890403674308</v>
+        <v>0.6663644346924544</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8454</v>
+        <v>8070</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>316.6837820252101</v>
+        <v>332.5927995438497</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>245</v>
+        <v>50.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,25 +3838,25 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.76348309572988</v>
+        <v>52.37414756318709</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.8364480554633</v>
+        <v>17.99171535684342</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7783361177141775</v>
+        <v>0.3688507308270164</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.030005806898202</v>
+        <v>0.0471160965222408</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8404</v>
+        <v>8114</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>316.3339330828437</v>
+        <v>331.1983370892369</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>16.2</v>
+        <v>194.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.46039269699298</v>
+        <v>44.45648848090541</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.23761031525907</v>
+        <v>16.76504061702536</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.193930709803198</v>
+        <v>0.5488164779930813</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0216682784207507</v>
+        <v>-0.597684189976694</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8422</v>
+        <v>8081</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>315.1920933603507</v>
+        <v>330.9335776669601</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>26.1</v>
+        <v>254.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.53435010005016</v>
+        <v>46.21201824036076</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.12001190292781</v>
+        <v>16.35835527211312</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6514667405349768</v>
+        <v>0.4230769927137641</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.08526083299075959</v>
+        <v>0.1238700063613356</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8121</v>
+        <v>8074</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>313.8165514654265</v>
+        <v>330.8895585119076</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>27.9</v>
+        <v>53.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>41.3218593855005</v>
+        <v>42.11775927115707</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>26.59894795389214</v>
+        <v>14.54973065921907</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5517656878953492</v>
+        <v>0.56942738539106</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.3594767953725513</v>
+        <v>0.0514017261715327</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8249</v>
+        <v>8440</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>311.2446363178515</v>
+        <v>328.7443273256742</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>40.95</v>
+        <v>20.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.25162841323826</v>
+        <v>49.01900444323775</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.26780483803184</v>
+        <v>18.79250106481216</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.09666842786995</v>
+        <v>0.5139961854855799</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1982117935250389</v>
+        <v>-0.000881403336585</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8104</v>
+        <v>8086</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>307.557014240904</v>
+        <v>321.6648800312735</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>30.65</v>
+        <v>112.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.71505337553143</v>
+        <v>43.51685422477986</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>22.69341096163254</v>
+        <v>17.80138400794277</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.730380980646131</v>
+        <v>0.5397824652365338</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.145638463478626</v>
+        <v>0.4275037627370879</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8932</v>
+        <v>8110</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>304.1954230947849</v>
+        <v>320.3516906715813</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>43.55</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.66987644388202</v>
+        <v>43.2906464250111</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.22825852586865</v>
+        <v>8.574052916699479</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6176620066683413</v>
+        <v>0.5519939799360098</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.889901590189257</v>
+        <v>-0.0835890403578847</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>9103</v>
+        <v>8045</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>301.9633976814756</v>
+        <v>319.0008493535788</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>5.14</v>
+        <v>50.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.03352196180453</v>
+        <v>40.11729468855427</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.738759834764087</v>
+        <v>12.58250274129647</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6997929943649973</v>
+        <v>1.986242253715627</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0059428405750496</v>
+        <v>0.0871338219277719</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8374</v>
+        <v>8454</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>292.2754634799531</v>
+        <v>316.6837820252101</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>81.7</v>
+        <v>245</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.00314965517635</v>
+        <v>41.76348320692187</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.43691960147952</v>
+        <v>10.8364480367179</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5286697288069971</v>
+        <v>0.7783361177141775</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.1677326387224153</v>
+        <v>-1.030005807852166</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8390</v>
+        <v>8404</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>291.658366937498</v>
+        <v>316.3339330828452</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>97</v>
+        <v>16.2</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.21192573071305</v>
+        <v>45.46039278557221</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.08180491421917</v>
+        <v>12.2376103589058</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8510809748712838</v>
+        <v>1.193930709803198</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1326508692086586</v>
+        <v>0.0216682784779874</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>9802</v>
+        <v>8422</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>288.2176422387431</v>
+        <v>315.1920933603507</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>72.3</v>
+        <v>26.1</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,49 +4368,49 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.88846424668173</v>
+        <v>42.53434977060948</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>9.356309867639467</v>
+        <v>12.12001191224315</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6975663484061568</v>
+        <v>0.6514667405349768</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1531239688788009</v>
+        <v>-0.0852608325002772</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8210</v>
+        <v>8121</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>287.1818007811553</v>
+        <v>313.8165514654265</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>986</v>
+        <v>27.9</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.58946964938312</v>
+        <v>41.32185944551206</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.12258062157996</v>
+        <v>26.59894795435223</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5836651782673049</v>
+        <v>0.5517656878953492</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>6.470871995636472</v>
+        <v>0.3594767952866902</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8046</v>
+        <v>8249</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>286.9251625578155</v>
+        <v>311.2446363178516</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1055</v>
+        <v>40.95</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.00462499037545</v>
+        <v>45.25162849501669</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.62491236434763</v>
+        <v>19.26780490639835</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.378223587994814</v>
+        <v>1.09666842786995</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-18.09155799904013</v>
+        <v>0.198211793277</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>9902</v>
+        <v>8213</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>284.9649003733161</v>
+        <v>310.2543602905096</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>13.65</v>
+        <v>32.95</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.09400164651691</v>
+        <v>52.01940878866883</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7.507726314263231</v>
+        <v>18.87086294340847</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4581693594666969</v>
+        <v>0.5821481877570361</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0179116503110662</v>
+        <v>0.0683749231471633</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8071</v>
+        <v>8104</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>282.9205611945055</v>
+        <v>307.557014240904</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>23.25</v>
+        <v>30.65</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.64801598403518</v>
+        <v>41.71505348772549</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.84414126178544</v>
+        <v>22.69341094243337</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3994840792057045</v>
+        <v>0.730380980646131</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.017263422366583</v>
+        <v>0.1456384632973703</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8227</v>
+        <v>9902</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>276.9840372683758</v>
+        <v>304.9649003733161</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>158.5</v>
+        <v>13.65</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.6970293260249</v>
+        <v>47.0940017497266</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.97657022669707</v>
+        <v>7.507726366995961</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3565676857653715</v>
+        <v>0.4581693594666969</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.9552863319826332</v>
+        <v>-0.0179116503587654</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8091</v>
+        <v>8932</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>271.1108235185746</v>
+        <v>304.1954230947849</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>215</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.79326919098445</v>
+        <v>38.66987664166481</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.47347159425082</v>
+        <v>17.22825864300657</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7770071797781976</v>
+        <v>0.6176620066683413</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.632982306924478</v>
+        <v>-1.88990159117023</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8076</v>
+        <v>8374</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>260.9379959646617</v>
+        <v>292.2754634799532</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>22.15</v>
+        <v>81.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>33.9356859110185</v>
+        <v>50.00314968895496</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.78098402776009</v>
+        <v>13.43691961500542</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.035637272306441</v>
+        <v>0.5286697288069971</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>1</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1015664718026082</v>
+        <v>-0.1677326389704383</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8162</v>
+        <v>8390</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>259.6502593002105</v>
+        <v>291.6583669374982</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>60.6</v>
+        <v>97</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>49.48047164542968</v>
+        <v>45.21192568263921</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.17912358166447</v>
+        <v>12.08180495263783</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.341783894550288</v>
+        <v>0.8510809748712838</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2487635373238804</v>
+        <v>-0.1326508690178628</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8088</v>
+        <v>8046</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>256.0936224359119</v>
+        <v>286.925162557816</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>43.15</v>
+        <v>1055</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>33.90614979799234</v>
+        <v>42.0046250072938</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.96265136387918</v>
+        <v>11.62491235564405</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6215935538758783</v>
+        <v>1.378223587994814</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>1</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0970111320422444</v>
+        <v>-18.09155799923093</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8131</v>
+        <v>8071</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>252.9282783497914</v>
+        <v>282.9205611945055</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>61.4</v>
+        <v>23.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>44.65464106483155</v>
+        <v>44.64801601929378</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8.12710680140955</v>
+        <v>11.8441413398446</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.527392375963886</v>
+        <v>0.3994840792057045</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.09278373568460969</v>
+        <v>-0.0172634224238191</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8467</v>
+        <v>8210</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>245.0622941165981</v>
+        <v>277.1818007811553</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>90.2</v>
+        <v>986</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>34.05392902217318</v>
+        <v>45.58946965122378</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.54983862883742</v>
+        <v>14.12258053248423</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.024812802818969</v>
+        <v>0.5836651782673049</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.2375826002129475</v>
+        <v>6.470871996399637</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8477</v>
+        <v>8227</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>240.6799185981747</v>
+        <v>276.9840372683759</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>15.25</v>
+        <v>158.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.59588305269001</v>
+        <v>50.69702936453946</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6.572142188033819</v>
+        <v>16.97657027772936</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4431226271672219</v>
+        <v>0.3565676857653715</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0467010227319938</v>
+        <v>0.9552863308378828</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>9904</v>
+        <v>8091</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>240.5382044114963</v>
+        <v>271.1108235185746</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>24.6</v>
+        <v>215</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.40464637401955</v>
+        <v>40.79326920057716</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.39127733932362</v>
+        <v>16.47347154561562</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.363611452817673</v>
+        <v>0.7770071797781976</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0142369883476667</v>
+        <v>0.6329823067336831</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8048</v>
+        <v>8076</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>236.9748778861257</v>
+        <v>260.9379959646617</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>51.6</v>
+        <v>22.15</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45.22006162726648</v>
+        <v>33.93568593105896</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.81249803369872</v>
+        <v>10.78098403286339</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8612268513327442</v>
+        <v>1.035637272306441</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1912123167425279</v>
+        <v>-0.1015664718598478</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8499</v>
+        <v>8088</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>236.121372961446</v>
+        <v>256.0936224359119</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>253</v>
+        <v>43.15</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.46353555247554</v>
+        <v>33.90614983098946</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.16993629556733</v>
+        <v>13.96265142291931</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.1450088717312063</v>
+        <v>0.6215935538758783</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.064716465223391</v>
+        <v>-0.0970111320994862</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8213</v>
+        <v>8131</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>235.2543602905097</v>
+        <v>252.9282783497914</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>32.95</v>
+        <v>61.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.01940877628157</v>
+        <v>44.65464108331857</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>18.87086297003108</v>
+        <v>8.12710680140955</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5821481877570361</v>
+        <v>0.527392375963886</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0683749231662427</v>
+        <v>0.09278373564644581</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8201</v>
+        <v>8467</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>234.01843045448</v>
+        <v>245.0622941165983</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>11.8</v>
+        <v>90.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46.07156652783619</v>
+        <v>34.05392905216431</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.12493413100752</v>
+        <v>11.54983861425555</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.002430332710813</v>
+        <v>1.024812802818969</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0168990573703438</v>
+        <v>-0.2375826008807324</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8092</v>
+        <v>8477</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>232.7813872953986</v>
+        <v>240.6799185981747</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>12.95</v>
+        <v>15.25</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.63757225273267</v>
+        <v>47.59588308008615</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.52925717192527</v>
+        <v>6.572142185807037</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3776048616459142</v>
+        <v>0.4431226271672219</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0414470387208174</v>
+        <v>-0.0467010227224563</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8059</v>
+        <v>8048</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>221.3874376668905</v>
+        <v>236.9748778861257</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>13.5</v>
+        <v>51.6</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.31048521729355</v>
+        <v>45.22006162726648</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.75569558562547</v>
+        <v>12.81249803603206</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5116367594428975</v>
+        <v>0.8612268513327442</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0403071412495287</v>
+        <v>0.1912123167234467</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>9955</v>
+        <v>8499</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>221.2106054664739</v>
+        <v>236.1213729614453</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>23.85</v>
+        <v>253</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.39245168998748</v>
+        <v>42.46353555732298</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.2350738984603</v>
+        <v>11.16993634741936</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6641041719956917</v>
+        <v>0.1450088717312063</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.08369190640105879</v>
+        <v>-1.064716464937209</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8049</v>
+        <v>8201</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>213.583907191229</v>
+        <v>234.0184304544811</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.45</v>
+        <v>11.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>34.82215486075401</v>
+        <v>46.07156654818947</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>22.54806661573138</v>
+        <v>18.12493413734106</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8235976494120455</v>
+        <v>1.002430332710813</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0149261728607855</v>
+        <v>0.0168990573608048</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8044</v>
+        <v>8092</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>211.733536470784</v>
+        <v>232.7813872953986</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>24</v>
+        <v>12.95</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>33.51012220666846</v>
+        <v>45.63757223911166</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.22300757717119</v>
+        <v>15.52925767426785</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.13103908324525</v>
+        <v>0.3776048616459142</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0990980754911934</v>
+        <v>0.041447038739897</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8478</v>
+        <v>8059</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>210.3599428822803</v>
+        <v>221.3874376668906</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>142</v>
+        <v>13.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.79031621232681</v>
+        <v>40.31048532302106</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.20537900761722</v>
+        <v>18.75569545965939</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5066151805207426</v>
+        <v>0.5116367594428975</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.3215894115737705</v>
+        <v>0.0403071411732133</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8045</v>
+        <v>9955</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>209.0008493535796</v>
+        <v>221.2106054664738</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>50.2</v>
+        <v>23.85</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.11729458593467</v>
+        <v>42.39245164805953</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.58250273487383</v>
+        <v>16.23507388321993</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.986242253715627</v>
+        <v>0.6641041719956917</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.08713382229027861</v>
+        <v>-0.0836919063724423</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8455</v>
+        <v>8463</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>208.4828952702093</v>
+        <v>213.723086013837</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>22.5</v>
+        <v>21.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.39292940986554</v>
+        <v>53.25491818729092</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.87655596862634</v>
+        <v>13.18593395170019</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>2.793104953087497</v>
+        <v>0.2227024794565418</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.2159228063112199</v>
+        <v>0.018930655209361</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8068</v>
+        <v>8049</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>208.0976134603769</v>
+        <v>213.5839071912291</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>16.85</v>
+        <v>24.45</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.13319873851538</v>
+        <v>34.82215480065355</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.06796441670806</v>
+        <v>22.54806676775683</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9653615625405884</v>
+        <v>0.8235976494120455</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0244739535216954</v>
+        <v>0.0149261728798646</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8466</v>
+        <v>8044</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>206.9411629692808</v>
+        <v>211.7335364707841</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>15.1</v>
+        <v>24</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>33.56008289682626</v>
+        <v>33.51012219162699</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>31.66941102856126</v>
+        <v>16.22300753754449</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6881313587164508</v>
+        <v>1.13103908324525</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0380570018080904</v>
+        <v>-0.0990980754816556</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8087</v>
+        <v>8478</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>204.7197812570221</v>
+        <v>210.3599428822803</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.97603902830762</v>
+        <v>43.79031642143435</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6.927590328365759</v>
+        <v>11.20537900761722</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2212650734342542</v>
+        <v>0.5066151805207426</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.07050233020966321</v>
+        <v>0.3215894107151826</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8047</v>
+        <v>8068</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>196.7431119525829</v>
+        <v>208.0976134603769</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>43</v>
+        <v>16.85</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>50.39981757793365</v>
+        <v>38.13319883747097</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>11.70711837979686</v>
+        <v>14.06796441670806</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.016722719752693</v>
+        <v>0.9653615625405884</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.563276952336631</v>
+        <v>0.0244739534549178</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8463</v>
+        <v>8466</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>193.723086013837</v>
+        <v>206.9411629692808</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>21.4</v>
+        <v>15.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.2549181622586</v>
+        <v>33.56008277507269</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.18593393698324</v>
+        <v>31.66941105467948</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2227024794565418</v>
+        <v>0.6881313587164508</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0189306552188993</v>
+        <v>-0.0380570017794726</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8341</v>
+        <v>8047</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>190.1624214396153</v>
+        <v>196.7431119525829</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>75.2</v>
+        <v>43</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.86430170004012</v>
+        <v>50.39981757996238</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>9.322089567501148</v>
+        <v>11.70711838692299</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.03269409567069</v>
+        <v>1.016722719752693</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1218333819896915</v>
+        <v>-0.563276952374792</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>9136</v>
+        <v>8341</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>183.3334821572932</v>
+        <v>190.1624214396153</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>11</v>
+        <v>75.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.60285844004036</v>
+        <v>40.86430168966662</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>9.075892439749008</v>
+        <v>9.322089569808854</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.1618904309044207</v>
+        <v>1.03269409567069</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0079980414017112</v>
+        <v>-0.1218333820087648</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8472</v>
+        <v>9136</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>183.0721713954265</v>
+        <v>183.3334821572932</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>11</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>56.21829449045472</v>
+        <v>42.60285843290541</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.7829756370588</v>
+        <v>9.075892557464931</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5701676863165457</v>
+        <v>0.1618904309044207</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,11 +6135,11 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.5367731169651377</v>
+        <v>-0.0079980413959877</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.52464191057258</v>
+        <v>44.52464193157456</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.5845309849188</v>
+        <v>19.58453100560617</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.4973659392076581</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0451508819604014</v>
+        <v>0.0451508817982254</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>37.98859502577723</v>
+        <v>37.98859206148322</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.68532983925768</v>
+        <v>10.6853292581319</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.3604720742284095</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0799660675439785</v>
+        <v>-0.0799660650350303</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.1445071012262</v>
+        <v>44.144507211699</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.91304782159723</v>
+        <v>12.91304776656195</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.8656688335196675</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0187197697008657</v>
+        <v>0.0187197696436267</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.91667210655351</v>
+        <v>38.91667209601964</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.2183715547751</v>
+        <v>11.21837155102009</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.843207870678876</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0092625109114646</v>
+        <v>-0.009262510882843999</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.8080105826651</v>
+        <v>37.80801074319383</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.47376189834197</v>
+        <v>24.47376186358014</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.2998689518719326</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1074816466100237</v>
+        <v>-0.1074816467912791</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.8860243103145</v>
+        <v>42.8860243796515</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.36668140140482</v>
+        <v>16.36668143697264</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.8557477057938966</v>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.37028590403313</v>
+        <v>38.3702859881528</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.93287022192777</v>
+        <v>11.93287031020467</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.8800844209275431</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0023136865360711</v>
+        <v>0.0023136865074523</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         <v>35.08665638781245</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.98741407835853</v>
+        <v>14.98741408641059</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.1558224642355193</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.095137910212361</v>
+        <v>0.0951379101932929</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.25039462620649</v>
+        <v>44.2503945995913</v>
       </c>
       <c r="I116" s="2" t="n">
         <v>15.0006281523876</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.3493361668693664</v>
+        <v>-0.349336166850289</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>105.2628322039634</v>
+        <v>105.2628322039635</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>17.05</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>34.69366194118975</v>
+        <v>34.69366202873903</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12.66442977678304</v>
+        <v>12.66442990202107</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.419288595526219</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0414892882231585</v>
+        <v>-0.0414892883471733</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
